--- a/docs/plan/Plan_RUP_SM-Xplore.xlsx
+++ b/docs/plan/Plan_RUP_SM-Xplore.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CARLOS\UNIVERSIDAD\ARQUITECTURA DE SOFTWARE\ACTIVIDAD N°1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dae\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86E9DF95-9DD2-0C4E-B984-4154177C4DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C118354-FEEC-4BAD-B46D-DDB688134712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{DB962AA2-3131-4457-BD0C-54827816F854}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB962AA2-3131-4457-BD0C-54827816F854}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -127,9 +127,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -208,10 +208,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -226,11 +226,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -238,9 +237,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -256,7 +255,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -553,27 +552,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BC6B996-FA04-4BB3-AE25-24FD1024F045}">
   <dimension ref="E3:R31"/>
-  <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="21.65625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.98828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.62109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="G3" s="13" t="s">
+    <row r="3" spans="5:18" x14ac:dyDescent="0.3">
+      <c r="G3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="5:18" x14ac:dyDescent="0.3">
       <c r="G4" s="6" t="s">
         <v>1</v>
       </c>
@@ -590,28 +587,28 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="10">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="H5" s="10">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="I5" s="10">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J5" s="10">
         <v>1100</v>
       </c>
       <c r="K5" s="10">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="6" spans="5:18" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E6" s="5" t="s">
         <v>7</v>
       </c>
@@ -629,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="5:18" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E7" s="5" t="s">
         <v>8</v>
       </c>
@@ -652,21 +649,21 @@
       <c r="K7" s="7">
         <v>1</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-    </row>
-    <row r="8" spans="5:18" x14ac:dyDescent="0.2">
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+    </row>
+    <row r="8" spans="5:18" x14ac:dyDescent="0.3">
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
@@ -677,7 +674,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E10" s="3" t="s">
         <v>10</v>
       </c>
@@ -694,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E11" s="2" t="s">
         <v>11</v>
       </c>
@@ -705,7 +702,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E12" s="2" t="s">
         <v>12</v>
       </c>
@@ -716,7 +713,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E13" s="3" t="s">
         <v>13</v>
       </c>
@@ -737,7 +734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
@@ -747,9 +744,8 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="11"/>
-    </row>
-    <row r="15" spans="5:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E15" s="2" t="s">
         <v>15</v>
       </c>
@@ -760,7 +756,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E16" s="2" t="s">
         <v>16</v>
       </c>
@@ -771,7 +767,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E17" s="4" t="s">
         <v>17</v>
       </c>
@@ -792,7 +788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E18" s="2" t="s">
         <v>18</v>
       </c>
@@ -803,7 +799,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E19" s="2" t="s">
         <v>19</v>
       </c>
@@ -814,7 +810,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E20" s="4" t="s">
         <v>20</v>
       </c>
@@ -833,7 +829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E21" s="2" t="s">
         <v>21</v>
       </c>
@@ -844,7 +840,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E22" s="2" t="s">
         <v>22</v>
       </c>
@@ -855,7 +851,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E23" s="2" t="s">
         <v>23</v>
       </c>
@@ -866,7 +862,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="25" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E25" s="2" t="s">
         <v>24</v>
       </c>
@@ -896,22 +892,22 @@
       </c>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="9">
         <f>G25*(G5/2)*G6*G7</f>
-        <v>4620</v>
+        <v>4125</v>
       </c>
       <c r="H26" s="9">
         <f>H25*(H5/2)*H6*H7</f>
-        <v>5400</v>
+        <v>5940</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" ref="H26:K26" si="1">I25*(I5/2)*I6*I7</f>
-        <v>1575</v>
+        <f t="shared" ref="I26:K26" si="1">I25*(I5/2)*I6*I7</f>
+        <v>1125</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
@@ -919,61 +915,61 @@
       </c>
       <c r="K26" s="9">
         <f t="shared" si="1"/>
-        <v>6160</v>
+        <v>2200</v>
       </c>
       <c r="L26" s="9">
         <f>SUM(G26:K26)</f>
-        <v>17755</v>
-      </c>
-    </row>
-    <row r="27" spans="5:18" x14ac:dyDescent="0.2">
+        <v>13390</v>
+      </c>
+    </row>
+    <row r="27" spans="5:18" x14ac:dyDescent="0.3">
       <c r="L27" s="9">
         <f>L26*0.1</f>
-        <v>1775.5</v>
-      </c>
-    </row>
-    <row r="28" spans="5:18" x14ac:dyDescent="0.2">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="28" spans="5:18" x14ac:dyDescent="0.3">
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="5:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="5:18" x14ac:dyDescent="0.3">
       <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="9">
         <f>SUM($L$26:$L$27)</f>
-        <v>19530.5</v>
-      </c>
-    </row>
-    <row r="30" spans="5:18" x14ac:dyDescent="0.2">
+        <v>14729</v>
+      </c>
+    </row>
+    <row r="30" spans="5:18" x14ac:dyDescent="0.3">
       <c r="K30" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L30" s="9">
         <f>L29*0.35 + L29</f>
-        <v>26366.174999999999</v>
-      </c>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-    </row>
-    <row r="31" spans="5:18" x14ac:dyDescent="0.2">
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
+        <v>19884.150000000001</v>
+      </c>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+    </row>
+    <row r="31" spans="5:18" x14ac:dyDescent="0.3">
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
